--- a/aq_files/0796.xlsx
+++ b/aq_files/0796.xlsx
@@ -1,101 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
-  <si>
-    <t>Q.No,Question,Type,Difficulty</t>
-  </si>
-  <si>
-    <t>1,What is mean Average Precision (mAP) in object detection? How is it calculated?,Technical,Medium</t>
-  </si>
-  <si>
-    <t>2,Explain the concepts of precision and recall in the context of object detection.,Theory,Easy</t>
-  </si>
-  <si>
-    <t>3,What is Intersection over Union (IoU)? How is it used in evaluation?,Technical,Easy</t>
-  </si>
-  <si>
-    <t>4,What is Average Precision (AP)? How is it computed from precision-recall curve?,Technical,Medium</t>
-  </si>
-  <si>
-    <t>5,What is the difference between AP@0.5, AP@0.75, and AP@[0.5:0.95] in COCO evaluation?,Technical,Medium</t>
-  </si>
-  <si>
-    <t>6,What is AP_small, AP_medium, and AP_large in COCO metrics?,Technical,Medium</t>
-  </si>
-  <si>
-    <t>7,What is AR (Average Recall) in object detection? How is it different from AP?,Technical,Medium</t>
-  </si>
-  <si>
-    <t>8,How do you compute F1 score for object detection?,Technical,Easy</t>
-  </si>
-  <si>
-    <t>9,What is the confusion matrix in object detection? How do you interpret it?,Technical,Medium</t>
-  </si>
-  <si>
-    <t>10,Write Python code to compute IoU between two bounding boxes.,Coding,Medium</t>
-  </si>
-  <si>
-    <t>11,Write Python code to calculate precision and recall for object detection predictions.,Coding,Hard</t>
-  </si>
-  <si>
-    <t>12,How do you implement Non-Maximum Suppression (NMS) evaluation metrics?,Coding,Hard</t>
-  </si>
-  <si>
-    <t>13,What is the difference between training metrics and evaluation metrics?,Theory,Medium</t>
-  </si>
-  <si>
-    <t>14,What is inference time (FPS) and how is it measured for object detectors?,Technical,Medium</t>
-  </si>
-  <si>
-    <t>15,What is model size and FLOPs? Why are they important for deployment?,Technical,Medium</t>
-  </si>
-  <si>
-    <t>16,How do you evaluate object detection models on edge devices?,Practical,Medium</t>
-  </si>
-  <si>
-    <t>17,What is the trade-off between accuracy and speed in object detection?,Theory,Easy</t>
-  </si>
-  <si>
-    <t>18,How do you compare different object detection models using standardized benchmarks?,Theory,Medium</t>
-  </si>
-  <si>
-    <t>19,What are the limitations of mAP as an evaluation metric?,Theory,Medium</t>
-  </si>
-  <si>
-    <t>20,Write Python code to generate a precision-recall curve for object detection results.,Coding,Hard</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -105,29 +38,87 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -325,118 +316,685 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="46.25" customWidth="1" style="2" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Operation</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Practical Question</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Command/Operation</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Output</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Error Scenario</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>git pull</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Pull latest changes from main branch before starting work</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>git pull origin main</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Local main updated to latest</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Prevents conflicts later</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>git merge</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Merge a team member's feature branch</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>git checkout main, git pull, git merge teammate-feature</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Feature merged into main</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>May have conflicts</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>git fetch + merge</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Fetch and merge remote branch (alternative to pull)</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>git fetch origin, git merge origin/feature</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Same as git pull</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>More control</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Pull Request</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Create Pull Request on GitHub for code review</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Push branch, GitHub UI → New Pull Request</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>PR created for review</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Team review process</t>
+        </is>
+      </c>
+      <c r="G5" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Code Review</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Review and comment on Pull Request</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>GitHub UI → Files changed → Add comment</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Comments added to code</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>git rebase</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Rebase feature branch on latest main before PR</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>git fetch origin, git rebase origin/main, git push --force-with-lease</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>Feature branch rebased</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>Clean history before merge</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>git stash</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>Stash changes when switching to review a PR</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>git stash, git checkout main, git pull, git checkout feature, git stash pop</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>Changes preserved during context switch</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>No commit needed</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>git cherry-pick</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>Apply specific commit from teammate's branch</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>git cherry-pick abc1234</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>Specific commit applied to current branch</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>Selective merging</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>git blame</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>Identify who last modified each line of code</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>git blame filename.py</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>Shows author and commit for each line</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>Code attribution</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>git log --author</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Find commits by specific team member</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>git log --author="John" --oneline</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>All commits by John</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>Code history tracking</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>git shortlog</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>Get summary of contributions per developer</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>git shortlog -sn</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>Count of commits per author</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>Team productivity view</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>Merge Conflict</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>Resolve merge conflict with team member</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>git pull, resolve conflicts in files, git add, git commit</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>Conflict resolved</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>Communication key</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>git diff</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>Review teammate's changes before merging</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>git fetch origin, git diff main origin/feature</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>Shows all changes in feature branch</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>Code review from terminal</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>git checkout</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>Switch to teammate's branch for testing</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>git fetch origin, git checkout -b teammate-feature origin/teammate-feature</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>Local copy of teammate's branch</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>Testing before merge</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="1" t="n">
         <v>15</v>
       </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>git remote add upstream</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>Add upstream remote for forked repositories</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>git remote add upstream original-repo-url</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>Upstream added</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>Keep fork updated</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>git pull --rebase</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>Sync fork with upstream without merge commits</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>git fetch upstream, git rebase upstream/main, git push --force-with-lease</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>Fork updated, clean history</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>Preferred for forks</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="1" t="n">
         <v>17</v>
       </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>git tag</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>Tag releases for team deployment</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>git tag -a v1.0 -m "Release version 1.0", git push --tags</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>Release tagged</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>Team versioning</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="1" t="n">
         <v>18</v>
       </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>git config user.name</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>Set different identity for work vs personal projects</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>git config user.name "Work Account" (in repo)</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>Commit attribution correct</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>Multiple identities</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="1" t="n">
         <v>19</v>
       </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>git bisect</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>Team debugging: find which commit introduced bug</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>git bisect start, git bisect bad, git bisect good v1.0</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>Bug-introducing commit found</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>Collaborative debugging</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="1" t="n">
         <v>20</v>
       </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>GitHub Issues</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>Create issue for bug tracking, assign to teammate</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>GitHub UI → Issues → New issue</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>Issue created, assigned</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>Task management</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>